--- a/2022_annualized_predictions_by_county.xlsx
+++ b/2022_annualized_predictions_by_county.xlsx
@@ -525,10 +525,10 @@
         <v>193093551.542332</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>220202770.527675</v>
+        <v>218791816.4136129</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>280769776.3230312</v>
+        <v>280769776.3230313</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>335149376</v>
@@ -540,10 +540,10 @@
         <v>353307904</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>241647776</v>
+        <v>286982176</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>244981984</v>
+        <v>297694208</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +562,10 @@
         <v>256171122.9459487</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>249668502.9165927</v>
+        <v>249595172.0654917</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>254789372.5730594</v>
+        <v>254789372.5730595</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>307632416</v>
@@ -577,10 +577,10 @@
         <v>307524000</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>247974304</v>
+        <v>270776928</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>206102208</v>
+        <v>256418656</v>
       </c>
     </row>
     <row r="4">
@@ -599,10 +599,10 @@
         <v>138008320.4686386</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>202088090.5269036</v>
+        <v>203425183.8098867</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>263037994.6844103</v>
+        <v>263037994.68441</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>320091744</v>
@@ -614,10 +614,10 @@
         <v>325107456</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>230737392</v>
+        <v>272286912</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>232145168</v>
+        <v>280323840</v>
       </c>
     </row>
     <row r="5">
@@ -636,10 +636,10 @@
         <v>265478249.3851308</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>328543889.0319309</v>
+        <v>335934961.2232968</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>220326424.9195888</v>
+        <v>220326424.9195887</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>265773200</v>
@@ -651,10 +651,10 @@
         <v>284477856</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>261647024</v>
+        <v>248927888</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>192629824</v>
+        <v>221992112</v>
       </c>
     </row>
     <row r="6">
@@ -673,10 +673,10 @@
         <v>254232957.3303978</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>280182067.5388317</v>
+        <v>285577323.5994892</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>186422949.2220211</v>
+        <v>186422949.222021</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>253879200</v>
@@ -688,10 +688,10 @@
         <v>255175920</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>214063808</v>
+        <v>203798960</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>169120448</v>
+        <v>194426896</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         <v>253353098.8901476</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>240485317.0089063</v>
+        <v>232266080.9118289</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>218634404.3398727</v>
+        <v>218634404.3398723</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>238115168</v>
@@ -725,10 +725,10 @@
         <v>235771184</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>214175488</v>
+        <v>218079056</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>168708912</v>
+        <v>219247776</v>
       </c>
     </row>
     <row r="8">
@@ -747,10 +747,10 @@
         <v>142984953.2165851</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>143427121.5530229</v>
+        <v>140247549.5425033</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>214635870.8837096</v>
+        <v>214635870.8837097</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>254392256</v>
@@ -762,10 +762,10 @@
         <v>230882432</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>192445648</v>
+        <v>243049456</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>217970880</v>
+        <v>253445504</v>
       </c>
     </row>
     <row r="9">
@@ -784,10 +784,10 @@
         <v>257126958.3615426</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>271277307.3424726</v>
+        <v>263382798.7891794</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>189454181.1367507</v>
+        <v>189454181.1367506</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>242992832</v>
@@ -799,10 +799,10 @@
         <v>228973040</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>208352448</v>
+        <v>183625312</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>143616544</v>
+        <v>178000960</v>
       </c>
     </row>
     <row r="10">
@@ -821,10 +821,10 @@
         <v>297824502.3513095</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>268458241.9210229</v>
+        <v>281844590.6932423</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>221234917.6816693</v>
+        <v>221234917.681669</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>252200192</v>
@@ -836,10 +836,10 @@
         <v>256179504</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>212240176</v>
+        <v>212959648</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>174934896</v>
+        <v>210424336</v>
       </c>
     </row>
     <row r="11">
@@ -858,7 +858,7 @@
         <v>224423905.8387325</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>268815035.2805673</v>
+        <v>273743204.8943222</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>216980286.198818</v>
@@ -873,10 +873,10 @@
         <v>244130080</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>217048576</v>
+        <v>218736672</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>174638560</v>
+        <v>206915488</v>
       </c>
     </row>
     <row r="12">
@@ -895,10 +895,10 @@
         <v>222031183.9951516</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>237870275.807649</v>
+        <v>231592200.2299547</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>231809060.2073062</v>
+        <v>231809060.2073063</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>250688896</v>
@@ -910,10 +910,10 @@
         <v>241425824</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>204445456</v>
+        <v>222906720</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>174796080</v>
+        <v>217852288</v>
       </c>
     </row>
     <row r="13">
@@ -932,7 +932,7 @@
         <v>206917158.6628184</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>242556996.3545364</v>
+        <v>241278816.9075812</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>215797097.0821037</v>
@@ -947,10 +947,10 @@
         <v>216169472</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>205576336</v>
+        <v>205588512</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>165406672</v>
+        <v>194680736</v>
       </c>
     </row>
     <row r="14">
@@ -969,7 +969,7 @@
         <v>235760417.4688847</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>239315463.2703556</v>
+        <v>236015093.6941059</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>212490458.6520107</v>
@@ -984,10 +984,10 @@
         <v>227156992</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>193521232</v>
+        <v>202311056</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>159173888</v>
+        <v>197045680</v>
       </c>
     </row>
     <row r="15">
@@ -1006,10 +1006,10 @@
         <v>195236227.1452472</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>194335566.7121153</v>
+        <v>192111741.236605</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>202792238.1640165</v>
+        <v>202792238.1640164</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>216380992</v>
@@ -1021,10 +1021,10 @@
         <v>203763264</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>191429632</v>
+        <v>198446624</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>161237328</v>
+        <v>189817952</v>
       </c>
     </row>
     <row r="16">
@@ -1043,10 +1043,10 @@
         <v>111612245.044827</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>117321689.4149228</v>
+        <v>114208851.9984896</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>183356033.7358561</v>
+        <v>183356033.7358562</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>226506464</v>
@@ -1058,10 +1058,10 @@
         <v>224488960</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>164116848</v>
+        <v>211002144</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>195785008</v>
+        <v>225029472</v>
       </c>
     </row>
     <row r="17">
@@ -1080,10 +1080,10 @@
         <v>127690861.9879499</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>112120065.9869202</v>
+        <v>118001572.3871126</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>192644715.7986157</v>
+        <v>192644715.7986153</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>225178160</v>
@@ -1095,10 +1095,10 @@
         <v>205988448</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>170339712</v>
+        <v>218058944</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>184156960</v>
+        <v>240093200</v>
       </c>
     </row>
     <row r="18">
@@ -1117,10 +1117,10 @@
         <v>266635386.0118019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>236623888.8096893</v>
+        <v>233953452.5495139</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>200026258.6290458</v>
+        <v>200026258.629046</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>208109024</v>
@@ -1132,10 +1132,10 @@
         <v>206191872</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>185814352</v>
+        <v>188590752</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>151976064</v>
+        <v>188371344</v>
       </c>
     </row>
     <row r="19">
@@ -1154,10 +1154,10 @@
         <v>270521915.7719574</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>218616462.7026921</v>
+        <v>232341002.2845162</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>196368512.1968326</v>
+        <v>196368512.1968324</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>207999408</v>
@@ -1169,10 +1169,10 @@
         <v>204319296</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>171580384</v>
+        <v>164740304</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>135855904</v>
+        <v>163546016</v>
       </c>
     </row>
     <row r="20">
@@ -1191,10 +1191,10 @@
         <v>174727146.7022159</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>186047097.4428453</v>
+        <v>189366245.1250422</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>139484499.5633659</v>
+        <v>139484499.5633662</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>172307632</v>
@@ -1206,10 +1206,10 @@
         <v>179020576</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>169684640</v>
+        <v>172535840</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>135582320</v>
+        <v>160722416</v>
       </c>
     </row>
     <row r="21">
@@ -1228,10 +1228,10 @@
         <v>231242629.3762765</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>215776507.9712587</v>
+        <v>209779161.9486149</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>199410334.6197302</v>
+        <v>199410334.6197303</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>199596672</v>
@@ -1243,10 +1243,10 @@
         <v>196758400</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>173817504</v>
+        <v>176895168</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>141567840</v>
+        <v>161976528</v>
       </c>
     </row>
     <row r="22">
@@ -1265,10 +1265,10 @@
         <v>96105015.09505686</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>106239646.7854391</v>
+        <v>110881417.1436498</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>156312603.3316741</v>
+        <v>156312603.3316742</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>200212464</v>
@@ -1280,10 +1280,10 @@
         <v>194695360</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>148514240</v>
+        <v>184134080</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>160155168</v>
+        <v>200063856</v>
       </c>
     </row>
     <row r="23">
@@ -1302,10 +1302,10 @@
         <v>189311592.3609789</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>159645037.6442368</v>
+        <v>160915838.819906</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>211413931.4704567</v>
+        <v>211413931.4704568</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>198400000</v>
@@ -1317,10 +1317,10 @@
         <v>189285792</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>169492544</v>
+        <v>194775504</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>165964720</v>
+        <v>201262576</v>
       </c>
     </row>
     <row r="24">
@@ -1339,10 +1339,10 @@
         <v>173207685.4986377</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>174434430.5255696</v>
+        <v>178076692.5781536</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>166687792.0752855</v>
+        <v>166687792.0752857</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>185044752</v>
@@ -1354,10 +1354,10 @@
         <v>179460816</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>171388960</v>
+        <v>177165696</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>151195200</v>
+        <v>179367216</v>
       </c>
     </row>
     <row r="25">
@@ -1376,7 +1376,7 @@
         <v>192653199.753359</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>196855430.3214391</v>
+        <v>193174379.7868701</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>202334991.9142914</v>
@@ -1391,10 +1391,10 @@
         <v>171188016</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>163439232</v>
+        <v>170222528</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>151143344</v>
+        <v>171177024</v>
       </c>
     </row>
     <row r="26">
@@ -1413,10 +1413,10 @@
         <v>161919232.4711429</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>171357154.1884638</v>
+        <v>175173717.7575531</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>155655490.044876</v>
+        <v>155655490.0448761</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>166541120</v>
@@ -1428,10 +1428,10 @@
         <v>162446960</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>167001520</v>
+        <v>178809200</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>150849504</v>
+        <v>174276720</v>
       </c>
     </row>
     <row r="27">
@@ -1450,10 +1450,10 @@
         <v>287441831.7675157</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>197088194.4324724</v>
+        <v>194162166.48797</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>163623776.9277599</v>
+        <v>163623776.9277597</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>181046608</v>
@@ -1465,10 +1465,10 @@
         <v>177169392</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>161267216</v>
+        <v>166419776</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>131776008</v>
+        <v>165182272</v>
       </c>
     </row>
     <row r="28">
@@ -1487,10 +1487,10 @@
         <v>156032178.8610449</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>166444066.5018185</v>
+        <v>165485869.8561225</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>161406312.2891262</v>
+        <v>161406312.289126</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>169386752</v>
@@ -1502,10 +1502,10 @@
         <v>160165312</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>160791408</v>
+        <v>168522288</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>144023856</v>
+        <v>168270640</v>
       </c>
     </row>
     <row r="29">
@@ -1524,7 +1524,7 @@
         <v>160724326.022191</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>173257336.0103423</v>
+        <v>168482341.0126635</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>158826868.0459737</v>
@@ -1539,10 +1539,10 @@
         <v>164334432</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>143776336</v>
+        <v>140856256</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>116347168</v>
+        <v>130791072</v>
       </c>
     </row>
     <row r="30">
@@ -1561,10 +1561,10 @@
         <v>159033587.9938005</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>168022633.7536868</v>
+        <v>172968557.6561743</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>147733289.2518557</v>
+        <v>147733289.2518556</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>158081472</v>
@@ -1576,10 +1576,10 @@
         <v>157027776</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>155229424</v>
+        <v>160855040</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>133719904</v>
+        <v>149497376</v>
       </c>
     </row>
     <row r="31">
@@ -1598,7 +1598,7 @@
         <v>145411982.4793988</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>155101923.9783993</v>
+        <v>157563863.7206166</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>139720376.470886</v>
@@ -1613,10 +1613,10 @@
         <v>153975808</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>150763024</v>
+        <v>163994544</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>131011128</v>
+        <v>157107328</v>
       </c>
     </row>
     <row r="32">
@@ -1635,10 +1635,10 @@
         <v>158697180.095498</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>155067092.3672998</v>
+        <v>156477506.1097471</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>164996442.3822972</v>
+        <v>164996442.3822974</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>167272400</v>
@@ -1650,10 +1650,10 @@
         <v>156579392</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>150599376</v>
+        <v>162978240</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>128309040</v>
+        <v>152817216</v>
       </c>
     </row>
     <row r="33">
@@ -1672,10 +1672,10 @@
         <v>171607349.2473879</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>164141454.5286474</v>
+        <v>157721024.5057872</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>147631721.8947358</v>
+        <v>147631721.8947359</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>166586400</v>
@@ -1687,10 +1687,10 @@
         <v>153459072</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>135680928</v>
+        <v>144810400</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>125132864</v>
+        <v>151408784</v>
       </c>
     </row>
     <row r="34">
@@ -1709,10 +1709,10 @@
         <v>148753331.157668</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>161162860.6030006</v>
+        <v>163244948.7833506</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>151452710.6668351</v>
+        <v>151452710.6668348</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>154222624</v>
@@ -1724,10 +1724,10 @@
         <v>144203904</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>148188064</v>
+        <v>159214064</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>137244592</v>
+        <v>158517568</v>
       </c>
     </row>
     <row r="35">
@@ -1746,10 +1746,10 @@
         <v>170670281.8092754</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>133543039.1318347</v>
+        <v>135482122.0802599</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>161624181.1315707</v>
+        <v>161624181.1315706</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>160807952</v>
@@ -1761,10 +1761,10 @@
         <v>142499728</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>141816416</v>
+        <v>150776640</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>132838760</v>
+        <v>148344496</v>
       </c>
     </row>
     <row r="36">
@@ -1783,7 +1783,7 @@
         <v>173823904.7936156</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>135356230.5109888</v>
+        <v>131939802.1150449</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>173142838.8171055</v>
@@ -1798,10 +1798,10 @@
         <v>135000288</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>136216512</v>
+        <v>170081824</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>142644880</v>
+        <v>159482912</v>
       </c>
     </row>
     <row r="37">
@@ -1820,7 +1820,7 @@
         <v>120972435.0359002</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>123878735.1500261</v>
+        <v>122787837.9725141</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>119504218.2571206</v>
@@ -1835,10 +1835,10 @@
         <v>124534288</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>127824624</v>
+        <v>140982976</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>119710520</v>
+        <v>129990752</v>
       </c>
     </row>
     <row r="38">
@@ -1857,10 +1857,10 @@
         <v>132338923.0147282</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>95874804.59536061</v>
+        <v>100749100.023751</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>135969364.678703</v>
+        <v>135969364.6787029</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>132714992</v>
@@ -1872,10 +1872,10 @@
         <v>120977760</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>125131880</v>
+        <v>138327040</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>131771416</v>
+        <v>138620032</v>
       </c>
     </row>
     <row r="39">
@@ -1894,10 +1894,10 @@
         <v>132809984.3146474</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>85005156.58745192</v>
+        <v>86732715.75026256</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>146265477.5211514</v>
+        <v>146265477.5211512</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>123696576</v>
@@ -1909,10 +1909,10 @@
         <v>115683016</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>119741592</v>
+        <v>148104320</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>131196432</v>
+        <v>148615648</v>
       </c>
     </row>
     <row r="40">
@@ -1931,10 +1931,10 @@
         <v>101609791.2231145</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>106226145.3609903</v>
+        <v>110427089.1036935</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>110099234.5993389</v>
+        <v>110099234.5993387</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>119990416</v>
@@ -1946,10 +1946,10 @@
         <v>111879184</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>105960288</v>
+        <v>119737848</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>102485000</v>
+        <v>106703208</v>
       </c>
     </row>
     <row r="41">
@@ -1968,7 +1968,7 @@
         <v>102431284.8968579</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>89039414.10911915</v>
+        <v>91475422.5148088</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>114786122.5989864</v>
@@ -1983,10 +1983,10 @@
         <v>109111880</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>116089336</v>
+        <v>127580832</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>123136808</v>
+        <v>130116640</v>
       </c>
     </row>
     <row r="42">
@@ -2005,7 +2005,7 @@
         <v>105226281.3881665</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>116054042.4330481</v>
+        <v>121302998.5330787</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>119892117.284548</v>
@@ -2020,10 +2020,10 @@
         <v>106981072</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>101850272</v>
+        <v>120765464</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>105559920</v>
+        <v>118891216</v>
       </c>
     </row>
     <row r="43">
@@ -2042,10 +2042,10 @@
         <v>96280360.52722885</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110005865.0936096</v>
+        <v>106095842.6708193</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>109868009.2695117</v>
+        <v>109868009.2695116</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>105037688</v>
@@ -2057,10 +2057,10 @@
         <v>101148400</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>93768024</v>
+        <v>101167424</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>94252464</v>
+        <v>89387376</v>
       </c>
     </row>
     <row r="44">
@@ -2079,10 +2079,10 @@
         <v>108808410.0754404</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109429565.4962746</v>
+        <v>108727361.9130284</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>124361497.808791</v>
+        <v>124361497.8087909</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>112028936</v>
@@ -2094,10 +2094,10 @@
         <v>100020368</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>110140944</v>
+        <v>127515488</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>120992344</v>
+        <v>124523120</v>
       </c>
     </row>
     <row r="45">
@@ -2116,7 +2116,7 @@
         <v>101030981.7255848</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>103387349.3469959</v>
+        <v>104464437.7120036</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>114259702.3126896</v>
@@ -2131,10 +2131,10 @@
         <v>100131168</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>101114320</v>
+        <v>110215928</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>97051896</v>
+        <v>104391280</v>
       </c>
     </row>
     <row r="46">
@@ -2153,10 +2153,10 @@
         <v>29900622.04367227</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>52059901.85099834</v>
+        <v>47034488.31518434</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>98519841.6297003</v>
+        <v>98519841.62970038</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>105991536</v>
@@ -2168,10 +2168,10 @@
         <v>95587088</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>101727888</v>
+        <v>125783328</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>120947272</v>
+        <v>143474624</v>
       </c>
     </row>
     <row r="47">
@@ -2190,10 +2190,10 @@
         <v>195127087.4443744</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>116413351.0252578</v>
+        <v>114007345.2885748</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>112872590.8785102</v>
+        <v>112872590.8785101</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>107048472</v>
@@ -2205,10 +2205,10 @@
         <v>100062440</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>105385552</v>
+        <v>125659840</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>103681096</v>
+        <v>132903432</v>
       </c>
     </row>
     <row r="48">
@@ -2227,10 +2227,10 @@
         <v>162598.2399805837</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>9611847.928850776</v>
+        <v>7830419.790537039</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>76483866.17032786</v>
+        <v>76483866.17032789</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>94977608</v>
@@ -2242,10 +2242,10 @@
         <v>91409640</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>79480704</v>
+        <v>111516528</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>152756640</v>
+        <v>162886304</v>
       </c>
     </row>
     <row r="49">
@@ -2264,10 +2264,10 @@
         <v>165134822.7393653</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104318955.2840845</v>
+        <v>106343081.8999301</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>111720441.0245979</v>
+        <v>111720441.0245977</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>96194152</v>
@@ -2279,10 +2279,10 @@
         <v>89502488</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>98976136</v>
+        <v>125104544</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>102303520</v>
+        <v>130623080</v>
       </c>
     </row>
     <row r="50">
@@ -2301,7 +2301,7 @@
         <v>106313274.6306003</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>95257676.1117281</v>
+        <v>95568662.14200212</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>103498231.8901967</v>
@@ -2316,10 +2316,10 @@
         <v>82453192</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>94270816</v>
+        <v>116424760</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>101024576</v>
+        <v>105931632</v>
       </c>
     </row>
     <row r="51">
@@ -2338,7 +2338,7 @@
         <v>118655993.3259431</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>100026322.7198127</v>
+        <v>101646693.2181792</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>102353051.3448942</v>
@@ -2353,10 +2353,10 @@
         <v>81200488</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>91605688</v>
+        <v>112551392</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>103464176</v>
+        <v>104074680</v>
       </c>
     </row>
     <row r="52">
@@ -2375,10 +2375,10 @@
         <v>83266038.52999219</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>84953011.86492139</v>
+        <v>87731029.28654942</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>77660692.89189488</v>
+        <v>77660692.8918948</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>83983488</v>
@@ -2390,10 +2390,10 @@
         <v>79244784</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>81517768</v>
+        <v>89251840</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>79967144</v>
+        <v>83924160</v>
       </c>
     </row>
     <row r="53">
@@ -2412,10 +2412,10 @@
         <v>92593577.11349267</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>87512441.05702764</v>
+        <v>84934870.55021524</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>102076214.0655943</v>
+        <v>102076214.0655942</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>83546128</v>
@@ -2427,10 +2427,10 @@
         <v>81182464</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>80037816</v>
+        <v>90708912</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>88988296</v>
+        <v>82336560</v>
       </c>
     </row>
     <row r="54">
@@ -2449,10 +2449,10 @@
         <v>73801570.62714127</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>75130996.99778485</v>
+        <v>74902177.52095941</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>67018663.96011509</v>
+        <v>67018663.96011506</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>72787240</v>
@@ -2464,10 +2464,10 @@
         <v>76544536</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>77644112</v>
+        <v>87570448</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>84066472</v>
+        <v>77149776</v>
       </c>
     </row>
     <row r="55">
@@ -2486,10 +2486,10 @@
         <v>67981938.35666831</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>66511551.44595024</v>
+        <v>71670088.31058648</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>80161558.20823884</v>
+        <v>80161558.20823871</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>72676832</v>
@@ -2501,10 +2501,10 @@
         <v>66308916</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>71325048</v>
+        <v>79523664</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>79760896</v>
+        <v>83669832</v>
       </c>
     </row>
     <row r="56">
@@ -2523,10 +2523,10 @@
         <v>69701811.20399332</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>71310481.88574935</v>
+        <v>68019966.65858951</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>81806535.06255673</v>
+        <v>81806535.06255661</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>65320760</v>
@@ -2538,10 +2538,10 @@
         <v>62943876</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>66218052</v>
+        <v>77038224</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>78586832</v>
+        <v>69025464</v>
       </c>
     </row>
     <row r="57">
@@ -2560,10 +2560,10 @@
         <v>56464932.46787849</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>56712392.78613409</v>
+        <v>58371853.43570008</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>51221223.63026252</v>
+        <v>51221223.63026253</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>51627408</v>
@@ -2575,10 +2575,10 @@
         <v>55773344</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>73047416</v>
+        <v>82162792</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>71796800</v>
+        <v>76747360</v>
       </c>
     </row>
     <row r="58">
@@ -2597,10 +2597,10 @@
         <v>43112654.1731187</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>45133039.97989151</v>
+        <v>45335913.78872987</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>51384005.36162902</v>
+        <v>51384005.36162898</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>43056260</v>
@@ -2612,10 +2612,10 @@
         <v>41402904</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>47272364</v>
+        <v>54907992</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>59737520</v>
+        <v>54676456</v>
       </c>
     </row>
     <row r="59">
@@ -2634,7 +2634,7 @@
         <v>62424085.17371069</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>55839802.08406415</v>
+        <v>56730855.24686717</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>57313398.62166574</v>
@@ -2649,10 +2649,10 @@
         <v>44747632</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>47707200</v>
+        <v>53449612</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>53240008</v>
+        <v>55086552</v>
       </c>
     </row>
     <row r="60">
@@ -2671,10 +2671,10 @@
         <v>26372113.35993765</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>31242916.20752365</v>
+        <v>33041166.76457961</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>33894971.14933937</v>
+        <v>33894971.14933936</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>28375916</v>
@@ -2686,10 +2686,10 @@
         <v>29484362</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31233400</v>
+        <v>37871504</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>30924632</v>
+        <v>34713000</v>
       </c>
     </row>
     <row r="61">
@@ -2708,7 +2708,7 @@
         <v>6546264.044122986</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12440310.95323475</v>
+        <v>11028884.1883705</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>24000357.91800689</v>
@@ -2723,10 +2723,10 @@
         <v>32357080</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>40660688</v>
+        <v>48468360</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>40503536</v>
+        <v>34616948</v>
       </c>
     </row>
     <row r="62">
@@ -2745,7 +2745,7 @@
         <v>19669878.75714861</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>19927309.73795787</v>
+        <v>22495089.7857841</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>26771183.35907517</v>
@@ -2760,10 +2760,10 @@
         <v>25174984</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>18276432</v>
+        <v>23039650</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>16786496</v>
+        <v>19669096</v>
       </c>
     </row>
     <row r="63">
@@ -2782,7 +2782,7 @@
         <v>24657835.16308882</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>26992249.59592843</v>
+        <v>25296142.26027718</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>21551062.6504129</v>
@@ -2797,10 +2797,10 @@
         <v>25674176</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>30803280</v>
+        <v>38322912</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>31859390</v>
+        <v>34258456</v>
       </c>
     </row>
     <row r="64">
@@ -2819,10 +2819,10 @@
         <v>19389549.797527</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>22277613.38410766</v>
+        <v>21468173.05836572</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>24833719.59353926</v>
+        <v>24833719.59353923</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>21348616</v>
@@ -2834,10 +2834,10 @@
         <v>23713740</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>20863888</v>
+        <v>23944362</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>22066264</v>
+        <v>22660046</v>
       </c>
     </row>
     <row r="65">
@@ -2856,10 +2856,10 @@
         <v>18719026.0168143</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>23843747.14039749</v>
+        <v>22751458.41374836</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>16929794.92631102</v>
+        <v>16929794.92631104</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>15620512</v>
@@ -2871,10 +2871,10 @@
         <v>18435738</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>20746024</v>
+        <v>21287186</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>25624674</v>
+        <v>23937794</v>
       </c>
     </row>
     <row r="66">
@@ -2893,7 +2893,7 @@
         <v>18749394.47566714</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>19443460.56208323</v>
+        <v>18630403.68479969</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>20137867.82811009</v>
@@ -2908,10 +2908,10 @@
         <v>17767068</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20353832</v>
+        <v>23754206</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>24069466</v>
+        <v>23636628</v>
       </c>
     </row>
     <row r="67">
@@ -2930,10 +2930,10 @@
         <v>16974162.09246362</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>15166506.32159883</v>
+        <v>15096793.0103695</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>18143392.9132987</v>
+        <v>18143392.91329867</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>14927646</v>
@@ -2945,10 +2945,10 @@
         <v>19328082</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12814284</v>
+        <v>14798015</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>18102908</v>
+        <v>21680156</v>
       </c>
     </row>
     <row r="68">
@@ -2967,10 +2967,10 @@
         <v>11683799.39242867</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>12452416.35924087</v>
+        <v>12485135.65414224</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>13703161.46381629</v>
+        <v>13703161.46381627</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>16435537</v>
@@ -2982,10 +2982,10 @@
         <v>20925442</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14190890</v>
+        <v>16367896</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>11843913</v>
+        <v>15766346</v>
       </c>
     </row>
     <row r="69">
@@ -3004,7 +3004,7 @@
         <v>13850252.63685296</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>12791264.1335573</v>
+        <v>11602866.04364736</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>15717329.35225981</v>
@@ -3019,10 +3019,10 @@
         <v>22830286</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>24548968</v>
+        <v>24877130</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>21001752</v>
+        <v>20156324</v>
       </c>
     </row>
     <row r="70">
@@ -3041,10 +3041,10 @@
         <v>18177527.53239848</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15719039.35373738</v>
+        <v>15420310.04003781</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>21738026.36533521</v>
+        <v>21738026.3653352</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>13731010</v>
@@ -3056,10 +3056,10 @@
         <v>17916938</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15408932</v>
+        <v>18102332</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>19369010</v>
+        <v>21234128</v>
       </c>
     </row>
     <row r="71">
@@ -3078,7 +3078,7 @@
         <v>8783275.659470003</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>10982360.30531237</v>
+        <v>10166732.20090318</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>12762936.70166199</v>
@@ -3093,10 +3093,10 @@
         <v>14855703</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>10891670</v>
+        <v>12622453</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>12035886</v>
+        <v>11177367</v>
       </c>
     </row>
     <row r="72">
@@ -3115,7 +3115,7 @@
         <v>14696085.05527324</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>16736333.60236925</v>
+        <v>16581737.35348916</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>10961500.82340573</v>
@@ -3130,10 +3130,10 @@
         <v>14190089</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>13066608</v>
+        <v>11649770</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>12648408</v>
+        <v>10843724</v>
       </c>
     </row>
     <row r="73">
@@ -3152,10 +3152,10 @@
         <v>25868752.24436354</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>14878132.95653328</v>
+        <v>14412663.64015262</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>8292435.009182028</v>
+        <v>8292435.009182024</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>6474600.5</v>
@@ -3167,10 +3167,10 @@
         <v>7047347</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>11896561</v>
+        <v>10165697</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>9775372</v>
+        <v>10278989</v>
       </c>
     </row>
     <row r="74">
@@ -3189,7 +3189,7 @@
         <v>7653684.005515673</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>8067727.078813635</v>
+        <v>7898132.517790945</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>8970363.416092101</v>
@@ -3204,10 +3204,10 @@
         <v>5641716.5</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>8637231</v>
+        <v>9694038</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>8975793</v>
+        <v>8581423</v>
       </c>
     </row>
     <row r="75">
@@ -3226,7 +3226,7 @@
         <v>7459568.039768897</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>3929847.252982755</v>
+        <v>4081474.982707805</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>8619201.42478021</v>
@@ -3241,10 +3241,10 @@
         <v>6826869</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>3902873</v>
+        <v>4001945.5</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2274205.5</v>
+        <v>3161844</v>
       </c>
     </row>
     <row r="76">
@@ -3263,10 +3263,10 @@
         <v>3545027.068324246</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>3866343.126058055</v>
+        <v>3818027.138260378</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>4096020.270093803</v>
+        <v>4096020.270093807</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>4008649</v>
@@ -3278,10 +3278,10 @@
         <v>3563536</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>4570120</v>
+        <v>4360458.5</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>3217350.25</v>
+        <v>3677225.25</v>
       </c>
     </row>
     <row r="77">
@@ -3300,10 +3300,10 @@
         <v>5693499.218176167</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>3539357.696410797</v>
+        <v>4062755.944270873</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>6218897.316536352</v>
+        <v>6218897.316536353</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>4225509.5</v>
@@ -3315,10 +3315,10 @@
         <v>7338377</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>3529644.25</v>
+        <v>3387274</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1601451.625</v>
+        <v>1996633.75</v>
       </c>
     </row>
     <row r="78">
@@ -3337,10 +3337,10 @@
         <v>1586260.513403529</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1665469.162891809</v>
+        <v>1436020.663370293</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2654976.270925148</v>
+        <v>2654976.270925147</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>1991530.375</v>
@@ -3352,10 +3352,10 @@
         <v>2095263</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1660019.125</v>
+        <v>1766863.5</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>929965.125</v>
+        <v>1083508.625</v>
       </c>
     </row>
     <row r="79">
@@ -3374,10 +3374,10 @@
         <v>2411882.236710215</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>956134.8822716011</v>
+        <v>1035012.875040577</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>2315672.230105642</v>
+        <v>2315672.230105644</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>1540746.75</v>
@@ -3389,10 +3389,10 @@
         <v>1484837.875</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1195777.25</v>
+        <v>1255665</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>828258.5</v>
+        <v>905142.5625</v>
       </c>
     </row>
     <row r="80">
@@ -3411,10 +3411,10 @@
         <v>13108919.34264534</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1300007.591221386</v>
+        <v>1418768.562799385</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>5491264.988866904</v>
+        <v>5491264.988866901</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>40630084</v>
@@ -3426,10 +3426,10 @@
         <v>1077421.375</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1520978.5</v>
+        <v>1397520.375</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1020534</v>
+        <v>793570.1875</v>
       </c>
     </row>
     <row r="81">
@@ -3448,10 +3448,10 @@
         <v>2108348.839717401</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1470699.169467316</v>
+        <v>1415760.398489749</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>1879966.188632141</v>
+        <v>1879966.18863214</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>1763890.625</v>
@@ -3463,10 +3463,10 @@
         <v>8255587.5</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2058471.125</v>
+        <v>2169351</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1551798.625</v>
+        <v>1990710.75</v>
       </c>
     </row>
     <row r="82">
@@ -3485,7 +3485,7 @@
         <v>2043845.023314729</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1432217.600990995</v>
+        <v>1324925.630548397</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>1293888.343087308</v>
@@ -3500,10 +3500,10 @@
         <v>1488362.75</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1802655.25</v>
+        <v>1917385.5</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1734134.25</v>
+        <v>1831684.75</v>
       </c>
     </row>
     <row r="83">
@@ -3522,10 +3522,10 @@
         <v>1215281.356110958</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>662317.1654341378</v>
+        <v>672400.8140382831</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>692205.54901775</v>
+        <v>692205.5490177504</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>668497.5</v>
@@ -3537,10 +3537,10 @@
         <v>1085429.75</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>847842.625</v>
+        <v>964014.5</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>675478.5625</v>
+        <v>640079.25</v>
       </c>
     </row>
     <row r="84">
@@ -3559,10 +3559,10 @@
         <v>359576.0363572013</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>551656.7754666783</v>
+        <v>529430.3071058579</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>604585.5197501867</v>
+        <v>604585.519750186</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>388142.625</v>
@@ -3574,10 +3574,10 @@
         <v>501675.9375</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>638471.9375</v>
+        <v>717161.8125</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>897035.25</v>
+        <v>593171</v>
       </c>
     </row>
   </sheetData>
